--- a/DATA/CARAVANAS MIGRANTES.xlsx
+++ b/DATA/CARAVANAS MIGRANTES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MEMORIA\MEMORIA CSP\INFORME MIGRATORIO 2024-25\CARAVANA MIGRANTES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bf48b3f04032ef9d/Documentos/SERVICIOS/PARKA/MIGRACIÓN/OFICINA/ALEX/IA-NAMI/BASES/DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC62CC5B-74B0-42F7-B589-362386A906C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{CC62CC5B-74B0-42F7-B589-362386A906C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92FAC0DC-FB3B-404D-A857-23795DA55638}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3EAF0B92-5813-4633-8BA5-1A19680C7D34}"/>
+    <workbookView xWindow="71880" yWindow="5265" windowWidth="29040" windowHeight="15720" xr2:uid="{3EAF0B92-5813-4633-8BA5-1A19680C7D34}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja2" sheetId="2" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>NOMBRE</t>
   </si>
@@ -118,6 +115,39 @@
   </si>
   <si>
     <t>Nueva caravana migrante</t>
+  </si>
+  <si>
+    <t>LUGAR DE DISOLUCIÓN</t>
+  </si>
+  <si>
+    <t>Chipehua, Oaxaca</t>
+  </si>
+  <si>
+    <t>Camron Yautepec, Oaxaca</t>
+  </si>
+  <si>
+    <t>San Blas Atempa, Oaxaca</t>
+  </si>
+  <si>
+    <t>La Ventosa, Oaxaca</t>
+  </si>
+  <si>
+    <t>Santo Domingo Zanatepec, Oaxaca</t>
+  </si>
+  <si>
+    <t>Escuintla, Chiapas</t>
+  </si>
+  <si>
+    <t>Mapastepec, Chiapas</t>
+  </si>
+  <si>
+    <t>Corazones, Oaxaca</t>
+  </si>
+  <si>
+    <t>Arriaga, Chiapas</t>
+  </si>
+  <si>
+    <t>Tonalá, Chiapas</t>
   </si>
 </sst>
 </file>
@@ -182,9 +212,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -222,7 +252,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -328,7 +358,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -470,7 +500,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -478,16 +508,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A082F854-FF12-461E-9589-3E5C494CD622}">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="1"/>
-    <col min="4" max="4" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.53125" style="1"/>
+    <col min="4" max="4" width="31.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -501,10 +532,13 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -517,11 +551,12 @@
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -534,11 +569,14 @@
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="1">
         <v>280</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -551,11 +589,14 @@
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="1">
         <v>770</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -568,11 +609,14 @@
       <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="1">
         <v>1789</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -585,11 +629,14 @@
       <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="1">
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -602,11 +649,12 @@
       <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
         <v>900</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -619,11 +667,12 @@
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
         <v>814</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -636,11 +685,12 @@
       <c r="D9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
         <v>950</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -653,11 +703,14 @@
       <c r="D10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="1">
         <v>1300</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -670,11 +723,14 @@
       <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="1">
         <v>980</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -687,11 +743,12 @@
       <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1">
         <v>243</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -704,11 +761,14 @@
       <c r="D13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="1">
         <v>635</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -721,11 +781,14 @@
       <c r="D14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -738,11 +801,14 @@
       <c r="D15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="1">
         <v>862</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -755,11 +821,12 @@
       <c r="D16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1">
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -772,11 +839,12 @@
       <c r="D17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
         <v>726</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -789,11 +857,14 @@
       <c r="D18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="1">
         <v>350</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -806,11 +877,12 @@
       <c r="D19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1">
         <v>980</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -823,11 +895,12 @@
       <c r="D20" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="1"/>
+      <c r="F20" s="1">
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -840,11 +913,12 @@
       <c r="D21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1">
         <v>190</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -857,11 +931,12 @@
       <c r="D22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1">
         <v>450</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -874,7 +949,8 @@
       <c r="D23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="1"/>
+      <c r="F23" s="1">
         <v>618</v>
       </c>
     </row>
